--- a/public/hierarchy-template.xlsx
+++ b/public/hierarchy-template.xlsx
@@ -1,59 +1,237 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="안내" sheetId="1" r:id="rId1"/>
-    <sheet name="등록" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="양식" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="필드" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="안내" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
+  <si>
+    <t>대분류</t>
+  </si>
+  <si>
+    <t>중분류</t>
+  </si>
+  <si>
+    <t>품목명</t>
+  </si>
+  <si>
+    <t>부제</t>
+  </si>
+  <si>
+    <t>상태</t>
+  </si>
+  <si>
+    <t>상태색</t>
+  </si>
+  <si>
+    <t>썸네일</t>
+  </si>
+  <si>
+    <t>면적</t>
+  </si>
+  <si>
+    <t>계약일</t>
+  </si>
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>라벨</t>
+  </si>
+  <si>
+    <t>종류</t>
+  </si>
+  <si>
+    <t>필수</t>
+  </si>
+  <si>
+    <t>배열</t>
+  </si>
+  <si>
+    <t>분류</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>배지</t>
+  </si>
+  <si>
+    <t>상태 색</t>
+  </si>
+  <si>
+    <t>배지색</t>
+  </si>
+  <si>
+    <t>숫자</t>
+  </si>
+  <si>
+    <t>날짜</t>
+  </si>
+  <si>
+    <t>이 파일 채우는 법 — 계층 등록표</t>
+  </si>
+  <si>
+    <t>「양식」 시트 한 장만 채우면 됩니다. 이 안내와 「필드」 시트는 설명·설정용입니다.</t>
+  </si>
+  <si>
+    <t>채우는 규칙</t>
+  </si>
+  <si>
+    <t>· 왼쪽 「대분류 / 중분류」가 폴더입니다. 왼쪽이 큰 분류, 오른쪽이 작은 분류.</t>
+  </si>
+  <si>
+    <t>· 같은 폴더에 품목이 여럿이면 폴더 칸을 똑같이 반복해 적으세요.</t>
+  </si>
+  <si>
+    <t>· 폴더만 먼저 만들려면 폴더 칸만 적고 「품목명」을 비워 두세요.</t>
+  </si>
+  <si>
+    <t>· 더 깊은 분류가 필요하면 「필드」 시트에 종류가 「분류」인 줄을 더하고, 「양식」에 그 열을 넣으세요.</t>
+  </si>
+  <si>
+    <t>예시 — 이 표를 「양식」 시트에 옮겨 적으면 이렇게 됩니다</t>
+  </si>
+  <si>
+    <t>현장</t>
+  </si>
+  <si>
+    <t>강남 현장</t>
+  </si>
+  <si>
+    <t>거실 도면</t>
+  </si>
+  <si>
+    <t>rev.2</t>
+  </si>
+  <si>
+    <t>승인</t>
+  </si>
+  <si>
+    <t>성공</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>주방 도면</t>
+  </si>
+  <si>
+    <t>rev.1</t>
+  </si>
+  <si>
+    <t>검토중</t>
+  </si>
+  <si>
+    <t>경고</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
+  </si>
+  <si>
+    <t>판교 현장</t>
+  </si>
+  <si>
+    <t>거래처</t>
+  </si>
+  <si>
+    <t>가구상사</t>
+  </si>
+  <si>
+    <t>계약서</t>
+  </si>
+  <si>
+    <t>확정</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>「판교 현장」 줄처럼 품목명을 비우면 폴더만 생깁니다.</t>
+  </si>
+  <si>
+    <t>「필드」 시트</t>
+  </si>
+  <si>
+    <t>· 「양식」의 각 열이 무엇인지 여기서 말합니다. 「이름」이 「양식」의 헤더와 같아야 합니다.</t>
+  </si>
+  <si>
+    <t>· 종류: 분류(폴더) · 글자 · 숫자 · 금액 · 날짜 · 퍼센트 · 예아니오 · 배지 · 배지색 · 썸네일</t>
+  </si>
+  <si>
+    <t>· 배지색에 적는 값: 성공 / 경고 / 위험 / 정보 / 기본. 비우면 기본입니다.</t>
+  </si>
+  <si>
+    <t>· 「품목명」 오른쪽 첫 열이 카드의 핵심값이 됩니다 — 중요한 지표를 앞에 두세요.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16181C"/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <color rgb="FF16181C"/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF9CA1AD"/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <color rgb="FF9CA1AD"/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4E4E4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -61,18 +239,70 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF16181C"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF6E7480"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF6E7480"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF6E7480"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF6E7480"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,273 +627,568 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="96.83203125" customWidth="1"/>
+    <col min="1" max="3" width="12" customWidth="1"/>
+    <col min="4" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>이 파일 채우는 법 — 먼저 읽어주세요</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>1. ‘등록’ 시트 한 장만 채우면 됩니다. (이 안내 시트는 설명용)</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2. 왼쪽 ‘대분류 / 중분류’ 칸에 폴더(분류)를 적으세요. 왼쪽이 큰 분류, 오른쪽이 작은 분류입니다.</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">     예) 대분류=현장,  중분류=강남 현장</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>3. 같은 폴더에 품목이 여러 개면, 폴더 칸을 똑같이 반복해 적고 ‘품목명’부터 오른쪽에 내용을 채우세요.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>4. 폴더만 먼저 만들고 싶으면 폴더 칸만 적고 ‘품목명’은 비워 두세요. (예시의 ‘판교 현장’ 줄)</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>5. 더 깊은 분류가 필요하면 ‘중분류’와 ‘품목명’ 사이에 칸을 끼워 넣으세요. 한 단계 더 깊어집니다.</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>6. 아래 예시 줄은 지우고 실제 데이터를 넣으세요.</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>입력값 안내</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>· 배지색: 성공 / 경고 / 위험 / 정보 / 기본 중 하나를 적으세요. (비우면 ‘기본’. ‘배지’ 칸이 비면 배지는 안 보입니다.)</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>· 헤더의 (숫자)(금액)(날짜)(퍼센트)(예아니오)는 그 칸에 넣을 값의 종류입니다. 헤더 글자는 바꾸지 마세요.</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>· 칸을 더 만들고 싶으면 맨 오른쪽에 「이름(숫자)」처럼 헤더를 추가하면 그 칸이 품목 정보로 들어갑니다.</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>· ‘품목명’ 열은 반드시 있어야 합니다. 지우지 마세요.</v>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A15"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E80"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>대분류</v>
-      </c>
-      <c r="B1" t="str">
-        <v>중분류</v>
-      </c>
-      <c r="C1" t="str">
-        <v>품목명</v>
-      </c>
-      <c r="D1" t="str">
-        <v>부제</v>
-      </c>
-      <c r="E1" t="str">
-        <v>배지</v>
-      </c>
-      <c r="F1" t="str">
-        <v>배지색</v>
-      </c>
-      <c r="G1" t="str">
-        <v>썸네일</v>
-      </c>
-      <c r="H1" t="str">
-        <v>면적(숫자)</v>
-      </c>
-      <c r="I1" t="str">
-        <v>계약일(날짜)</v>
-      </c>
-      <c r="J1" t="str">
-        <v>담당</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>현장</v>
-      </c>
-      <c r="B2" t="str">
-        <v>강남 현장</v>
-      </c>
-      <c r="C2" t="str">
-        <v>거실 도면</v>
-      </c>
-      <c r="D2" t="str">
-        <v>rev.2</v>
-      </c>
-      <c r="E2" t="str">
-        <v>승인</v>
-      </c>
-      <c r="F2" t="str">
-        <v>성공</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="C10:C80">
+      <formula1>"분류,이름,부제,배지,배지색,썸네일,글자,숫자,금액,날짜,퍼센트,예아니오"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C80">
+      <formula1>"분류,이름,부제,배지,배지색,썸네일,글자,숫자,금액,날짜,퍼센트,예아니오"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D80">
+      <formula1>"필수"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D80">
+      <formula1>"필수"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="26" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="10" ht="26" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="str">
-        <v>2026-05-02</v>
-      </c>
-      <c r="J2" t="str">
-        <v>김병준</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>현장</v>
-      </c>
-      <c r="B3" t="str">
-        <v>강남 현장</v>
-      </c>
-      <c r="C3" t="str">
-        <v>주방 도면</v>
-      </c>
-      <c r="D3" t="str">
-        <v>rev.1</v>
-      </c>
-      <c r="E3" t="str">
-        <v>검토중</v>
-      </c>
-      <c r="F3" t="str">
-        <v>경고</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3">
+      <c r="E12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="8">
+        <v>32</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="8">
         <v>18</v>
       </c>
-      <c r="I3" t="str">
-        <v>2026-05-10</v>
-      </c>
-      <c r="J3" t="str">
-        <v>이수연</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>현장</v>
-      </c>
-      <c r="B4" t="str">
-        <v>판교 현장</v>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>거래처</v>
-      </c>
-      <c r="B5" t="str">
-        <v>가구상사</v>
-      </c>
-      <c r="C5" t="str">
-        <v>계약서</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5" t="str">
-        <v>확정</v>
-      </c>
-      <c r="F5" t="str">
-        <v>성공</v>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-04-01</v>
-      </c>
-      <c r="J5" t="str">
-        <v>박지훈</v>
+      <c r="H13" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="26" customHeight="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>